--- a/goanna_burrow_detection.xlsx
+++ b/goanna_burrow_detection.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Time taken to find the burrow</t>
+          <t>Time spent searching for a burrow, whether or not one was found</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dig_or_inspect</t>
+          <t>burrow_found</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Was the burrow dug or just inspected?</t>
+          <t>Was a burrow found?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -745,52 +745,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple found_choices</t>
+          <t>select_one dig_or_inspect_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what_did_you_find</t>
+          <t>dig_or_inspect</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What did you find?</t>
+          <t>Was the burrow dug or just inspected?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
+          <t>${burrow_found} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>select_multiple found_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>what_did_you_find</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What did you find?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>${burrow_found} = 'Yes' and ${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>what_did_you_find_other</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Please specify</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>selected(${what_did_you_find}, 'other')</t>
         </is>

--- a/goanna_burrow_detection.xlsx
+++ b/goanna_burrow_detection.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -483,22 +483,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Session ID</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Auto-generated ID grouping all records from one hunting session</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -510,17 +505,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>location_lat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GPS latitude, captured when the search is stopped</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>location_lat</t>
+          <t>location_lon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GPS latitude</t>
+          <t>GPS longitude, captured when the search is stopped</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -559,22 +559,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one nta_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>location_lon</t>
+          <t>native_title_area</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>GPS longitude</t>
+          <t>Native title area</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -586,17 +581,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one nta_choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>native_title_area</t>
+          <t>hunting_team_names</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Native title area</t>
+          <t>Hunting team member names</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -608,17 +603,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hunting_team_names</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hunting team member names</t>
+          <t>Search start time</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -630,17 +625,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>record_number</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Start time</t>
+          <t>Record number</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -657,12 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>record_number</t>
+          <t>duration_seconds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Record number</t>
+          <t>Duration (seconds)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Time spent searching for a burrow, whether or not one was found</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>duration_seconds</t>
+          <t>people_searching</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Duration (seconds)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Time spent searching for a burrow, whether or not one was found</t>
+          <t>Number of people searching</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,17 +696,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>people_searching</t>
+          <t>burnt_area</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Number of people searching</t>
+          <t>Was this a burnt area?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -723,7 +718,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one dig_or_inspect_choices</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -745,7 +740,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one dig_or_inspect_choices</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -755,7 +750,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Was the burrow dug or just inspected?</t>
+          <t>Was the burrow inspected?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -772,52 +767,79 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple found_choices</t>
+          <t>select_one inspect_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what_did_you_find</t>
+          <t>inspection_method</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What did you find?</t>
+          <t>How was the burrow inspected?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>${burrow_found} = 'Yes' and ${dig_or_inspect} = 'Yes'</t>
+          <t>${dig_or_inspect} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>select_multiple found_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>what_did_you_find</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What did you find?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>what_did_you_find_other</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Please specify</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>selected(${what_did_you_find}, 'other')</t>
         </is>
@@ -834,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -861,7 +883,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dig_or_inspect_choices</t>
+          <t>yes_no_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -878,7 +900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dig_or_inspect_choices</t>
+          <t>yes_no_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -895,34 +917,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>found_choices</t>
+          <t>inspect_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nothing</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>found_choices</t>
+          <t>inspect_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goanna</t>
+          <t>dig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Goanna</t>
+          <t>Dig</t>
         </is>
       </c>
     </row>
@@ -934,12 +956,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bluetongue</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bluetongue</t>
+          <t>Nothing</t>
         </is>
       </c>
     </row>
@@ -951,12 +973,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>king_brown</t>
+          <t>spiny_tailed_goanna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>King Brown</t>
+          <t>Spiny-tailed goanna</t>
         </is>
       </c>
     </row>
@@ -968,78 +990,146 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>sand_goanna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sand goanna</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nta_choices</t>
+          <t>found_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>northern_bluetongue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Not on a native title area</t>
+          <t>Northern blue tongue (black one)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nta_choices</t>
+          <t>found_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTA-KJ</t>
+          <t>centralian_bluetongue</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Karajarri</t>
+          <t>Centralian blue tongue (yellow one)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nta_choices</t>
+          <t>found_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTA-NYKJ</t>
+          <t>king_brown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyangumarta-Karajarri shared country</t>
+          <t>King Brown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>found_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>nta_choices</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not on a native title area</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nta_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NTA-KJ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Karajarri</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>nta_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTA-NYKJ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nyangumarta-Karajarri shared country</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>nta_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>NTA-NY</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Nyangumarta</t>
         </is>

--- a/goanna_burrow_detection.xlsx
+++ b/goanna_burrow_detection.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -559,17 +559,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one nta_choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>native_title_area</t>
+          <t>hunting_team_names</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Native title area</t>
+          <t>Hunting team member names</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hunting_team_names</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hunting team member names</t>
+          <t>Search start time</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -603,17 +603,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>record_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Search start time</t>
+          <t>Record number</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -630,12 +630,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>record_number</t>
+          <t>duration_seconds</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Record number</t>
+          <t>Duration (seconds)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Time spent searching for a burrow, whether or not one was found</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +657,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>duration_seconds</t>
+          <t>people_searching</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duration (seconds)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Time spent searching for a burrow, whether or not one was found</t>
+          <t>Number of people searching</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>people_searching</t>
+          <t>burnt_area</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Number of people searching</t>
+          <t>Was this a burnt area?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>burnt_area</t>
+          <t>burrow_found</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Was this a burnt area?</t>
+          <t>Was a burrow found?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -723,34 +723,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>burrow_found</t>
+          <t>dig_or_inspect</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Was a burrow found?</t>
+          <t>Was the burrow inspected?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>${burrow_found} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one yes_no_choices</t>
+          <t>select_one inspect_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dig_or_inspect</t>
+          <t>inspection_method</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Was the burrow inspected?</t>
+          <t>How was the burrow inspected?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -760,29 +765,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>${burrow_found} = 'Yes'</t>
+          <t>${dig_or_inspect} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one inspect_method_choices</t>
+          <t>select_multiple found_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>inspection_method</t>
+          <t>what_did_you_find</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How was the burrow inspected?</t>
+          <t>What did you find?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -794,17 +799,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple found_choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>what_did_you_find</t>
+          <t>what_did_you_find_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What did you find?</t>
+          <t>Please specify</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -813,33 +818,6 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>what_did_you_find_other</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Please specify</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>selected(${what_did_you_find}, 'other')</t>
         </is>
@@ -856,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1064,74 +1042,6 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>nta_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Not on a native title area</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>nta_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NTA-KJ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Karajarri</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>nta_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NTA-NYKJ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nyangumarta-Karajarri shared country</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>nta_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NTA-NY</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nyangumarta</t>
         </is>
       </c>
     </row>

--- a/goanna_burrow_detection.xlsx
+++ b/goanna_burrow_detection.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -559,61 +559,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>geotrace</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hunting_team_names</t>
+          <t>search_track</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hunting team member names</t>
+          <t>Search track</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auto-recorded GPS track of the search</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>search_track_seconds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Search start time</t>
+          <t>Search track point times (elapsed seconds)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>record_number</t>
+          <t>hunting_team_names</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Record number</t>
+          <t>Hunting team member names</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,22 +630,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>duration_seconds</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duration (seconds)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Time spent searching for a burrow, whether or not one was found</t>
+          <t>Search start time</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>people_searching</t>
+          <t>record_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Number of people searching</t>
+          <t>Record number</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,17 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one yes_no_choices</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>burnt_area</t>
+          <t>duration_seconds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Was this a burnt area?</t>
+          <t>Duration (seconds)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Time spent searching for a burrow, whether or not one was found</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -696,17 +701,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one yes_no_choices</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>burrow_found</t>
+          <t>people_searching</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Was a burrow found?</t>
+          <t>Number of people searching</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -723,101 +728,145 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dig_or_inspect</t>
+          <t>burnt_area</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Was the burrow inspected?</t>
+          <t>Was this a burnt area?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>${burrow_found} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one inspect_method_choices</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inspection_method</t>
+          <t>burrow_found</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How was the burrow inspected?</t>
+          <t>Was a burrow found?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple found_choices</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what_did_you_find</t>
+          <t>dig_or_inspect</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What did you find?</t>
+          <t>Was the burrow inspected?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
+          <t>${burrow_found} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>select_one inspect_method_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>inspection_method</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How was the burrow inspected?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_multiple found_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>what_did_you_find</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What did you find?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>what_did_you_find_other</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Please specify</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>selected(${what_did_you_find}, 'other')</t>
         </is>

--- a/goanna_burrow_detection.xlsx
+++ b/goanna_burrow_detection.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,11 @@
           <t>relevant</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -767,17 +772,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one yes_no_choices</t>
+          <t>select_one burrow_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dig_or_inspect</t>
+          <t>burrow_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Was the burrow inspected?</t>
+          <t>What type of burrow?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -788,87 +793,168 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>${burrow_found} = 'Yes'</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>wandidji</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one inspect_method_choices</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>inspection_method</t>
+          <t>burrow_type_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How was the burrow inspected?</t>
+          <t>Please specify</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
+          <t>${burrow_type} = 'other'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple found_choices</t>
+          <t>select_one yes_no_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>what_did_you_find</t>
+          <t>dig_or_inspect</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What did you find?</t>
+          <t>Was the burrow inspected?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>${dig_or_inspect} = 'Yes'</t>
+          <t>${burrow_found} = 'Yes'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>select_one inspect_method_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>inspection_method</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How was the burrow inspected?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_multiple found_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>what_did_you_find</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What did you find?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>${dig_or_inspect} = 'Yes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>what_did_you_find_other</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Please specify</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>selected(${what_did_you_find}, 'other')</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -883,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1089,6 +1175,57 @@
         </is>
       </c>
       <c r="C12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>burrow_type_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>wandidji</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wandidji (V. acanthurus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>burrow_type_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>wanggali</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wanggali (V. gouldii)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>burrow_type_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
